--- a/analytics/reports/ticketflicks_analytics_report.xlsx
+++ b/analytics/reports/ticketflicks_analytics_report.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹7,500.00</t>
+          <t>₹8,781.00</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹500.00</t>
+          <t>₹585.40</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>₹1,250.00</t>
+          <t>₹878.10</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-05 00:24:33</t>
+          <t>2026-03-06 00:42:26</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,18 +717,38 @@
           <t>total_spent</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6978a7149c3b5dc208ba268d</t>
+          <t>69a9c33fc33095b555984eeb</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2000</v>
+        <v>1317</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kabir Verma</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>customer6990@example.com</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -743,6 +763,16 @@
       <c r="C3" t="n">
         <v>1100</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aarav Sharma</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>aaravsharma683@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -756,6 +786,16 @@
       <c r="C4" t="n">
         <v>1100</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>priyapatel282@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,6 +809,16 @@
       <c r="C5" t="n">
         <v>1100</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Aditya Verma</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adityaverma745@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -782,6 +832,16 @@
       <c r="C6" t="n">
         <v>1100</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Neha Reddy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>nehareddy847@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -794,6 +854,108 @@
       </c>
       <c r="C7" t="n">
         <v>1100</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rohan Desai</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rohandesai204@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984ee8</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>618</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Diya Patel</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>customer6187@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984ee9</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>510</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rohan Gupta</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>customer5689@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984eea</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>447</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Neha Singh</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>customer8107@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984ee7</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>389</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Aarav Sharma</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>customer2246@example.com</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -807,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,24 +991,57 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>800</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="B3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6700</v>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -913,95 +1108,103 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>69a54b5c442b1451606b555d</t>
+          <t>69a87f227287871ef58e1da7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6978a7149c3b5dc208ba268d</t>
+          <t>69a87f227287871ef58e1d98</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>69a3358c179d8faa9ad34e40</t>
+          <t>69a8780375d9b89273915b89</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>800</v>
+        <v>550</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="n">
-        <v>46083.35663039351</v>
+        <v>46085.78558711806</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>69a7f0d6065c17c59119001b</t>
+          <t>69a87f227287871ef58e1dae</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6978a7149c3b5dc208ba268d</t>
+          <t>69a87f227287871ef58e1d98</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>69a6cb1affde849a03dbfbc5</t>
+          <t>69a877ff75d9b89273915b2c</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
       <c r="I3" s="1" t="n">
-        <v>46085.3639657176</v>
+        <v>46085.78558873843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>69a80158ef903b13a6931eea</t>
+          <t>69a87f227287871ef58e1db5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6978a7149c3b5dc208ba268d</t>
+          <t>69a87f227287871ef58e1d9a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>69a6cb1affde849a03dbfbc2</t>
+          <t>69a8780175d9b89273915b4c</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1014,31 +1217,35 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
       <c r="I4" s="1" t="n">
-        <v>46085.41287819445</v>
+        <v>46085.78558971065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>69a80158ef903b13a6931eee</t>
+          <t>69a87f237287871ef58e1dbc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6978a7149c3b5dc208ba268d</t>
+          <t>69a87f227287871ef58e1d9a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>69a6cb1affde849a03dbfbc2</t>
+          <t>69a8780275d9b89273915b6a</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1051,31 +1258,35 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
       <c r="I5" s="1" t="n">
-        <v>46085.41287850695</v>
+        <v>46085.78559078704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69a80158ef903b13a6931ef2</t>
+          <t>69a87f237287871ef58e1dc3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6978a7149c3b5dc208ba268d</t>
+          <t>69a87f227287871ef58e1d9e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69a6cb1affde849a03dbfbc2</t>
+          <t>69a8780475d9b89273915ba6</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1088,27 +1299,31 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
       <c r="I6" s="1" t="n">
-        <v>46085.41287925926</v>
+        <v>46085.78559186342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1da7</t>
+          <t>69a87f237287871ef58e1dca</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1d98</t>
+          <t>69a87f227287871ef58e1d9e</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69a8780375d9b89273915b89</t>
+          <t>69a8780775d9b89273915c00</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1133,23 +1348,23 @@
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>46085.78558711806</v>
+        <v>46085.78559314815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1dae</t>
+          <t>69a87f237287871ef58e1dd1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1d98</t>
+          <t>69a87f227287871ef58e1da0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>69a877ff75d9b89273915b2c</t>
+          <t>69a877ff75d9b89273915b2b</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1174,23 +1389,23 @@
         </is>
       </c>
       <c r="I8" s="1" t="n">
-        <v>46085.78558873843</v>
+        <v>46085.78559429398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1db5</t>
+          <t>69a87f237287871ef58e1dd8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1d9a</t>
+          <t>69a87f227287871ef58e1da0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>69a8780175d9b89273915b4c</t>
+          <t>69a8780575d9b89273915bc1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1215,23 +1430,23 @@
         </is>
       </c>
       <c r="I9" s="1" t="n">
-        <v>46085.78558971065</v>
+        <v>46085.78559533565</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dbc</t>
+          <t>69a87f237287871ef58e1ddf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1d9a</t>
+          <t>69a87f227287871ef58e1da2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>69a8780275d9b89273915b6a</t>
+          <t>69a8780475d9b89273915ba6</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1256,23 +1471,23 @@
         </is>
       </c>
       <c r="I10" s="1" t="n">
-        <v>46085.78559078704</v>
+        <v>46085.78559663195</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dc3</t>
+          <t>69a87f237287871ef58e1de6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1d9e</t>
+          <t>69a87f227287871ef58e1da2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>69a8780475d9b89273915ba6</t>
+          <t>69a8780875d9b89273915c1e</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1297,212 +1512,172 @@
         </is>
       </c>
       <c r="I11" s="1" t="n">
-        <v>46085.78559186342</v>
+        <v>46085.78559770833</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dca</t>
+          <t>69a9c340c33095b555984eec</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1d9e</t>
+          <t>69a9c33fc33095b555984ee7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>69a8780775d9b89273915c00</t>
+          <t>69a8780175d9b89273915b48</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>550</v>
+        <v>389</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>46085.78559314815</v>
+        <v>46086.74592653936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dd1</t>
+          <t>69a9c340c33095b555984eed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1da0</t>
+          <t>69a9c33fc33095b555984ee8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>69a877ff75d9b89273915b2b</t>
+          <t>69a8780675d9b89273915bec</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" s="1" t="n">
-        <v>46085.78559429398</v>
+        <v>46085.74592653936</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dd8</t>
+          <t>69a9c340c33095b555984eee</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1da0</t>
+          <t>69a9c33fc33095b555984ee9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>69a8780575d9b89273915bc1</t>
+          <t>69a8780275d9b89273915b6d</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" s="1" t="n">
-        <v>46085.78559533565</v>
+        <v>46084.74592653936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1ddf</t>
+          <t>69a9c340c33095b555984eef</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1da2</t>
+          <t>69a9c33fc33095b555984eea</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>69a8780475d9b89273915ba6</t>
+          <t>69a8780375d9b89273915b86</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>550</v>
+        <v>447</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>46085.78559663195</v>
+        <v>46083.74592653936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1de6</t>
+          <t>69a9c340c33095b555984ef0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1da2</t>
+          <t>69a9c33fc33095b555984eeb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>69a8780875d9b89273915c1e</t>
+          <t>69a8780075d9b89273915b46</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>550</v>
+        <v>1317</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" s="1" t="n">
-        <v>46085.78559770833</v>
+        <v>46082.74592653936</v>
       </c>
     </row>
   </sheetData>
@@ -11537,7 +11712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12050,6 +12225,136 @@
       </c>
       <c r="F17" s="1" t="n">
         <v>46085.78558376157</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984ee7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aarav Sharma</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>customer2246@example.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>46086.74592559028</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984ee8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Diya Patel</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>customer6187@example.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>46086.74592559028</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984ee9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rohan Gupta</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>customer5689@example.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46086.74592559028</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984eea</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Neha Singh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>customer8107@example.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>46086.74592559028</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>69a9c33fc33095b555984eeb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabir Verma</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>customer6990@example.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>46086.74592559028</v>
       </c>
     </row>
   </sheetData>
@@ -12131,78 +12436,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>69a54b5c442b1451606b555d</t>
+          <t>69a87f227287871ef58e1da7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Test Admin</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>admin@test.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>aaravsharma683@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In the Lost Lands</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PVR Forum Mall Koramangala</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>46086.70833333334</v>
+      </c>
       <c r="H2" t="n">
-        <v>800</v>
+        <v>550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>69a7f0d6065c17c59119001b</t>
+          <t>69a87f227287871ef58e1dae</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Test Admin</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>admin@test.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>aaravsharma683@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Thunderbolts*</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INOX R-City Mall</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>46086.33333333334</v>
+      </c>
       <c r="H3" t="n">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>46085</v>
@@ -12211,25 +12544,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>69a80158ef903b13a6931eea</t>
+          <t>69a87f227287871ef58e1db5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Test Admin</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>admin@test.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>priyapatel282@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Devara: Part 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PVR Directors Cut Select City Walk</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>46086.58333333334</v>
+      </c>
       <c r="H4" t="n">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -12242,7 +12589,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>46085</v>
@@ -12251,25 +12598,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>69a80158ef903b13a6931eee</t>
+          <t>69a87f237287871ef58e1dbc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Test Admin</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>admin@test.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>priyapatel282@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Devara: Part 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>INOX DLF Promenade</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>46086.58333333334</v>
+      </c>
       <c r="H5" t="n">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -12282,7 +12643,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>46085</v>
@@ -12291,25 +12652,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>69a80158ef903b13a6931ef2</t>
+          <t>69a87f237287871ef58e1dc3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Test Admin</t>
+          <t>Aditya Verma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>admin@test.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>adityaverma745@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Devara: Part 1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PVR ICONX GVK One Mall</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>46086.58333333334</v>
+      </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -12322,7 +12697,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>46085</v>
@@ -12331,36 +12706,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1da7</t>
+          <t>69a87f237287871ef58e1dca</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Aditya Verma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>aaravsharma683@gmail.com</t>
+          <t>adityaverma745@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>In the Lost Lands</t>
+          <t>Devara: Part 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PVR Forum Mall Koramangala</t>
+          <t>PVR Phoenix Marketcity Pune</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46086.70833333334</v>
+        <v>46086.58333333334</v>
       </c>
       <c r="H7" t="n">
         <v>550</v>
@@ -12385,22 +12760,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1dae</t>
+          <t>69a87f237287871ef58e1dd1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Neha Reddy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>aaravsharma683@gmail.com</t>
+          <t>nehareddy847@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thunderbolts*</t>
+          <t>Mission: Impossible - The Final Reckoning</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -12414,7 +12789,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46086.33333333334</v>
+        <v>46086.1875</v>
       </c>
       <c r="H8" t="n">
         <v>550</v>
@@ -12439,36 +12814,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>69a87f227287871ef58e1db5</t>
+          <t>69a87f237287871ef58e1dd8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Neha Reddy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>priyapatel282@gmail.com</t>
+          <t>nehareddy847@gmail.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Devara: Part 1</t>
+          <t>Mission: Impossible - The Final Reckoning</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PVR Directors Cut Select City Walk</t>
+          <t>PVR VR Chennai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46086.58333333334</v>
+        <v>46086.1875</v>
       </c>
       <c r="H9" t="n">
         <v>550</v>
@@ -12493,17 +12868,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dbc</t>
+          <t>69a87f237287871ef58e1ddf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Rohan Desai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>priyapatel282@gmail.com</t>
+          <t>rohandesai204@gmail.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12513,12 +12888,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>INOX DLF Promenade</t>
+          <t>PVR ICONX GVK One Mall</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G10" s="1" t="n">
@@ -12547,17 +12922,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dc3</t>
+          <t>69a87f237287871ef58e1de6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aditya Verma</t>
+          <t>Rohan Desai</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>adityaverma745@gmail.com</t>
+          <t>rohandesai204@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12567,12 +12942,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PVR ICONX GVK One Mall</t>
+          <t>PVR Acropolis Mall</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="G11" s="1" t="n">
@@ -12601,104 +12976,96 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dca</t>
+          <t>69a9c340c33095b555984eec</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aditya Verma</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>adityaverma745@gmail.com</t>
+          <t>customer2246@example.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Devara: Part 1</t>
+          <t>Until Dawn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PVR Phoenix Marketcity Pune</t>
+          <t>INOX R-City Mall</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46086.58333333334</v>
+        <v>46091.70833333334</v>
       </c>
       <c r="H12" t="n">
-        <v>550</v>
+        <v>389</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dd1</t>
+          <t>69a9c340c33095b555984eed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neha Reddy</t>
+          <t>Diya Patel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nehareddy847@gmail.com</t>
+          <t>customer6187@example.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mission: Impossible - The Final Reckoning</t>
+          <t>Until Dawn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>INOX R-City Mall</t>
+          <t>Sathyam Cinemas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46086.1875</v>
+        <v>46088.58333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>550</v>
+        <v>618</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>2</v>
       </c>
@@ -12709,125 +13076,117 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1dd8</t>
+          <t>69a9c340c33095b555984eee</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Neha Reddy</t>
+          <t>Rohan Gupta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nehareddy847@gmail.com</t>
+          <t>customer5689@example.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mission: Impossible - The Final Reckoning</t>
+          <t>Lilo &amp; Stitch</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PVR VR Chennai</t>
+          <t>INOX DLF Promenade</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46086.1875</v>
+        <v>46087.33333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>46085</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1ddf</t>
+          <t>69a9c340c33095b555984eef</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rohan Desai</t>
+          <t>Neha Singh</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rohandesai204@gmail.com</t>
+          <t>customer8107@example.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Devara: Part 1</t>
+          <t>Thunderbolts*</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PVR ICONX GVK One Mall</t>
+          <t>PVR Forum Mall Koramangala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46086.58333333334</v>
+        <v>46086.33333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>550</v>
+        <v>447</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>46085</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>69a87f237287871ef58e1de6</t>
+          <t>69a9c340c33095b555984ef0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohan Desai</t>
+          <t>Kabir Verma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rohandesai204@gmail.com</t>
+          <t>customer6990@example.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12837,35 +13196,31 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PVR Acropolis Mall</t>
+          <t>INOX R-City Mall</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46086.58333333334</v>
+        <v>46091.45833333334</v>
       </c>
       <c r="H16" t="n">
-        <v>550</v>
+        <v>1317</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>46085</v>
+        <v>46082</v>
       </c>
     </row>
   </sheetData>
@@ -12879,7 +13234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12911,13 +13266,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3300</v>
+        <v>4617</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -12939,17 +13294,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>In the Lost Lands</t>
+          <t>Until Dawn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>550</v>
+        <v>1007</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -12959,12 +13314,44 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>In the Lost Lands</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>550</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lilo &amp; Stitch</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>510</v>
+      </c>
+      <c r="D7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12979,7 +13366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12990,15 +13377,20 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>bookings</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>seats_sold</t>
         </is>
@@ -13010,14 +13402,19 @@
           <t>INOX R-City Mall</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>1100</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2806</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -13026,13 +13423,18 @@
           <t>PVR ICONX GVK One Mall</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1100</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13042,93 +13444,144 @@
           <t>INOX DLF Promenade</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>550</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1060</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PVR Acropolis Mall</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>PVR Forum Mall Koramangala</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>550</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>997</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PVR Directors Cut Select City Walk</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+          <t>Sathyam Cinemas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>550</v>
-      </c>
       <c r="D6" t="n">
+        <v>618</v>
+      </c>
+      <c r="E6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PVR Forum Mall Koramangala</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>PVR Acropolis Mall</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>550</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PVR Phoenix Marketcity Pune</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+          <t>PVR Directors Cut Select City Walk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>550</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>PVR Phoenix Marketcity Pune</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>550</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>PVR VR Chennai</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D10" t="n">
         <v>550</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
     </row>

--- a/analytics/reports/ticketflicks_analytics_report.xlsx
+++ b/analytics/reports/ticketflicks_analytics_report.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -671,7 +671,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-06 00:42:26</t>
+          <t>2026-03-06 23:14:33</t>
         </is>
       </c>
     </row>
@@ -1518,21 +1518,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eec</t>
+          <t>69a9c340c33095b555984eed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>69a9c33fc33095b555984ee7</t>
+          <t>69a9c33fc33095b555984ee8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>69a8780175d9b89273915b48</t>
+          <t>69a8780675d9b89273915bec</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>389</v>
+        <v>618</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1545,27 +1545,27 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="n">
-        <v>46086.74592653936</v>
+        <v>46085.74592653936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eed</t>
+          <t>69a9c340c33095b555984ef0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>69a9c33fc33095b555984ee8</t>
+          <t>69a9c33fc33095b555984eeb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>69a8780675d9b89273915bec</t>
+          <t>69a8780075d9b89273915b46</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>618</v>
+        <v>1317</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1578,27 +1578,27 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" s="1" t="n">
-        <v>46085.74592653936</v>
+        <v>46082.74592653936</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eee</t>
+          <t>69a9c340c33095b555984eef</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>69a9c33fc33095b555984ee9</t>
+          <t>69a9c33fc33095b555984eea</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>69a8780275d9b89273915b6d</t>
+          <t>69a8780375d9b89273915b86</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1611,27 +1611,27 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" s="1" t="n">
-        <v>46084.74592653936</v>
+        <v>46083.74592653936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eef</t>
+          <t>69a9c340c33095b555984eec</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>69a9c33fc33095b555984eea</t>
+          <t>69a9c33fc33095b555984ee7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>69a8780375d9b89273915b86</t>
+          <t>69a8780175d9b89273915b48</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1644,27 +1644,27 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" s="1" t="n">
-        <v>46083.74592653936</v>
+        <v>46086.74592653936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984ef0</t>
+          <t>69a9c340c33095b555984eee</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>69a9c33fc33095b555984eeb</t>
+          <t>69a9c33fc33095b555984ee9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>69a8780075d9b89273915b46</t>
+          <t>69a8780275d9b89273915b6d</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1317</v>
+        <v>510</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" s="1" t="n">
-        <v>46082.74592653936</v>
+        <v>46084.74592653936</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Action, Fantasy, Western</t>
+          <t>Action, Fantasy, Western, Adventure</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
         <v>102</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46081.77083333334</v>
+        <v>46081</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -2361,7 +2361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2387,15 +2387,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>basePrice</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>totalCapacity</t>
         </is>
@@ -2420,15 +2425,16 @@
       <c r="D2" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
         <v>250</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2451,15 +2457,16 @@
       <c r="D3" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
         <v>300</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>160</v>
       </c>
     </row>
@@ -2482,15 +2489,16 @@
       <c r="D4" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
         <v>200</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>216</v>
       </c>
     </row>
@@ -2513,15 +2521,16 @@
       <c r="D5" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
         <v>180</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>140</v>
       </c>
     </row>
@@ -2544,15 +2553,16 @@
       <c r="D6" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
         <v>250</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2575,15 +2585,16 @@
       <c r="D7" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
         <v>250</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2606,15 +2617,16 @@
       <c r="D8" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
         <v>300</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>160</v>
       </c>
     </row>
@@ -2637,15 +2649,16 @@
       <c r="D9" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
         <v>200</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>216</v>
       </c>
     </row>
@@ -2668,15 +2681,16 @@
       <c r="D10" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
         <v>180</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>140</v>
       </c>
     </row>
@@ -2699,15 +2713,16 @@
       <c r="D11" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
         <v>250</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2730,15 +2745,16 @@
       <c r="D12" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
         <v>250</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2761,15 +2777,16 @@
       <c r="D13" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
         <v>300</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>160</v>
       </c>
     </row>
@@ -2792,15 +2809,16 @@
       <c r="D14" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
         <v>200</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>216</v>
       </c>
     </row>
@@ -2823,15 +2841,16 @@
       <c r="D15" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
         <v>180</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>140</v>
       </c>
     </row>
@@ -2854,15 +2873,16 @@
       <c r="D16" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
         <v>250</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2885,15 +2905,16 @@
       <c r="D17" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
         <v>250</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2916,15 +2937,16 @@
       <c r="D18" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
         <v>300</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>160</v>
       </c>
     </row>
@@ -2947,15 +2969,16 @@
       <c r="D19" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
         <v>200</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>216</v>
       </c>
     </row>
@@ -2978,15 +3001,16 @@
       <c r="D20" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
         <v>180</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>140</v>
       </c>
     </row>
@@ -3009,15 +3033,16 @@
       <c r="D21" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
         <v>250</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>280</v>
       </c>
     </row>
@@ -3040,15 +3065,16 @@
       <c r="D22" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
         <v>250</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>280</v>
       </c>
     </row>
@@ -3071,15 +3097,16 @@
       <c r="D23" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
         <v>300</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3102,15 +3129,16 @@
       <c r="D24" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
         <v>200</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>216</v>
       </c>
     </row>
@@ -3133,15 +3161,16 @@
       <c r="D25" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
         <v>180</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
         <v>140</v>
       </c>
     </row>
@@ -3164,15 +3193,16 @@
       <c r="D26" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
         <v>250</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>280</v>
       </c>
     </row>
@@ -3195,15 +3225,16 @@
       <c r="D27" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
         <v>250</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>280</v>
       </c>
     </row>
@@ -3226,15 +3257,16 @@
       <c r="D28" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
         <v>300</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3257,15 +3289,16 @@
       <c r="D29" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
         <v>200</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>216</v>
       </c>
     </row>
@@ -3288,15 +3321,16 @@
       <c r="D30" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
         <v>180</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>140</v>
       </c>
     </row>
@@ -3319,15 +3353,16 @@
       <c r="D31" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
         <v>250</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>280</v>
       </c>
     </row>
@@ -3350,15 +3385,16 @@
       <c r="D32" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
         <v>300</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3381,15 +3417,16 @@
       <c r="D33" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
         <v>150</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3412,15 +3449,16 @@
       <c r="D34" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
         <v>150</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3443,15 +3481,16 @@
       <c r="D35" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
         <v>200</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>96</v>
       </c>
     </row>
@@ -3474,15 +3513,16 @@
       <c r="D36" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
         <v>300</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3505,15 +3545,16 @@
       <c r="D37" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
         <v>300</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3536,15 +3577,16 @@
       <c r="D38" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
         <v>150</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3567,15 +3609,16 @@
       <c r="D39" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
         <v>150</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3598,15 +3641,20 @@
       <c r="D40" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>200</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
         <v>96</v>
       </c>
     </row>
@@ -3629,15 +3677,16 @@
       <c r="D41" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
         <v>300</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3660,15 +3709,16 @@
       <c r="D42" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
         <v>300</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3691,15 +3741,16 @@
       <c r="D43" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
         <v>150</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3722,15 +3773,16 @@
       <c r="D44" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
         <v>150</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3753,15 +3805,16 @@
       <c r="D45" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
         <v>200</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
         <v>96</v>
       </c>
     </row>
@@ -3784,15 +3837,16 @@
       <c r="D46" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
         <v>300</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3815,15 +3869,16 @@
       <c r="D47" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
         <v>300</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3846,15 +3901,16 @@
       <c r="D48" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
         <v>150</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3877,15 +3933,16 @@
       <c r="D49" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
         <v>150</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
         <v>192</v>
       </c>
     </row>
@@ -3908,15 +3965,16 @@
       <c r="D50" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
         <v>200</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
         <v>96</v>
       </c>
     </row>
@@ -3939,15 +3997,16 @@
       <c r="D51" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
         <v>300</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3970,15 +4029,16 @@
       <c r="D52" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
         <v>300</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
         <v>160</v>
       </c>
     </row>
@@ -4001,15 +4061,16 @@
       <c r="D53" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
         <v>150</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
         <v>192</v>
       </c>
     </row>
@@ -4032,15 +4093,16 @@
       <c r="D54" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
         <v>150</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
         <v>192</v>
       </c>
     </row>
@@ -4063,15 +4125,16 @@
       <c r="D55" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
         <v>200</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4094,15 +4157,16 @@
       <c r="D56" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
         <v>300</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
         <v>160</v>
       </c>
     </row>
@@ -4125,15 +4189,16 @@
       <c r="D57" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
         <v>300</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
         <v>160</v>
       </c>
     </row>
@@ -4156,15 +4221,16 @@
       <c r="D58" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
         <v>150</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
         <v>192</v>
       </c>
     </row>
@@ -4187,15 +4253,16 @@
       <c r="D59" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
         <v>150</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
         <v>192</v>
       </c>
     </row>
@@ -4218,15 +4285,16 @@
       <c r="D60" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="n">
         <v>200</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4249,15 +4317,20 @@
       <c r="D61" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>300</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
         <v>160</v>
       </c>
     </row>
@@ -4280,15 +4353,16 @@
       <c r="D62" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
         <v>200</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4311,15 +4385,16 @@
       <c r="D63" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
         <v>200</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4342,15 +4417,16 @@
       <c r="D64" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
         <v>150</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4373,15 +4449,16 @@
       <c r="D65" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
         <v>150</v>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4404,15 +4481,16 @@
       <c r="D66" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
         <v>200</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4435,15 +4513,16 @@
       <c r="D67" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
         <v>200</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4466,15 +4545,16 @@
       <c r="D68" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
         <v>200</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4497,15 +4577,16 @@
       <c r="D69" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
         <v>150</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4528,15 +4609,16 @@
       <c r="D70" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
         <v>150</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4559,15 +4641,16 @@
       <c r="D71" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
         <v>200</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4590,15 +4673,16 @@
       <c r="D72" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
         <v>200</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4621,15 +4705,16 @@
       <c r="D73" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
         <v>200</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4652,15 +4737,16 @@
       <c r="D74" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
         <v>150</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4683,15 +4769,16 @@
       <c r="D75" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
         <v>150</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4714,15 +4801,16 @@
       <c r="D76" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
         <v>200</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4745,15 +4833,16 @@
       <c r="D77" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
         <v>200</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4776,15 +4865,16 @@
       <c r="D78" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
         <v>200</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4807,15 +4897,16 @@
       <c r="D79" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
         <v>150</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4838,15 +4929,16 @@
       <c r="D80" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
         <v>150</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4869,15 +4961,16 @@
       <c r="D81" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
         <v>200</v>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4900,15 +4993,16 @@
       <c r="D82" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
         <v>200</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4931,15 +5025,16 @@
       <c r="D83" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
         <v>200</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
         <v>96</v>
       </c>
     </row>
@@ -4962,15 +5057,16 @@
       <c r="D84" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
         <v>150</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
         <v>140</v>
       </c>
     </row>
@@ -4993,15 +5089,16 @@
       <c r="D85" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
         <v>150</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5024,15 +5121,16 @@
       <c r="D86" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
         <v>200</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
         <v>96</v>
       </c>
     </row>
@@ -5055,15 +5153,16 @@
       <c r="D87" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
         <v>200</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
         <v>96</v>
       </c>
     </row>
@@ -5086,15 +5185,16 @@
       <c r="D88" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
         <v>200</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
         <v>96</v>
       </c>
     </row>
@@ -5117,15 +5217,16 @@
       <c r="D89" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
         <v>150</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5148,15 +5249,16 @@
       <c r="D90" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
         <v>150</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5179,15 +5281,16 @@
       <c r="D91" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
         <v>200</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
         <v>96</v>
       </c>
     </row>
@@ -5210,15 +5313,16 @@
       <c r="D92" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
         <v>250</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5241,15 +5345,16 @@
       <c r="D93" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
         <v>200</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5272,15 +5377,16 @@
       <c r="D94" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
         <v>150</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5303,15 +5409,16 @@
       <c r="D95" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
         <v>150</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5334,15 +5441,16 @@
       <c r="D96" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
         <v>250</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5365,15 +5473,16 @@
       <c r="D97" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
         <v>250</v>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5396,15 +5505,16 @@
       <c r="D98" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
         <v>200</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5427,15 +5537,16 @@
       <c r="D99" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
         <v>150</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5458,15 +5569,16 @@
       <c r="D100" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
         <v>150</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5489,15 +5601,16 @@
       <c r="D101" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
         <v>250</v>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5520,15 +5633,16 @@
       <c r="D102" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
         <v>250</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5551,15 +5665,16 @@
       <c r="D103" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="n">
         <v>200</v>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5582,15 +5697,16 @@
       <c r="D104" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="n">
         <v>150</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5613,15 +5729,16 @@
       <c r="D105" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
         <v>150</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5644,15 +5761,16 @@
       <c r="D106" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
         <v>250</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5675,15 +5793,16 @@
       <c r="D107" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
         <v>250</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5706,15 +5825,16 @@
       <c r="D108" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
         <v>200</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5737,15 +5857,16 @@
       <c r="D109" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
         <v>150</v>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5768,15 +5889,16 @@
       <c r="D110" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
         <v>150</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5799,15 +5921,16 @@
       <c r="D111" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
         <v>250</v>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5830,15 +5953,16 @@
       <c r="D112" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
         <v>250</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5861,15 +5985,16 @@
       <c r="D113" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
         <v>200</v>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
         <v>140</v>
       </c>
     </row>
@@ -5892,15 +6017,16 @@
       <c r="D114" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
         <v>150</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5923,15 +6049,16 @@
       <c r="D115" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
         <v>150</v>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
         <v>192</v>
       </c>
     </row>
@@ -5954,15 +6081,16 @@
       <c r="D116" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="n">
         <v>250</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
         <v>280</v>
       </c>
     </row>
@@ -5985,15 +6113,16 @@
       <c r="D117" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
         <v>250</v>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6016,15 +6145,16 @@
       <c r="D118" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
         <v>200</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
         <v>140</v>
       </c>
     </row>
@@ -6047,15 +6177,16 @@
       <c r="D119" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="n">
         <v>150</v>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6078,15 +6209,16 @@
       <c r="D120" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
         <v>150</v>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6109,15 +6241,16 @@
       <c r="D121" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
         <v>250</v>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G121" t="n">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6140,15 +6273,16 @@
       <c r="D122" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
         <v>250</v>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G122" t="n">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6171,15 +6305,16 @@
       <c r="D123" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
         <v>180</v>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G123" t="n">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6202,15 +6337,16 @@
       <c r="D124" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
         <v>150</v>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G124" t="n">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6233,15 +6369,16 @@
       <c r="D125" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
         <v>150</v>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6264,15 +6401,16 @@
       <c r="D126" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="n">
         <v>150</v>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
         <v>140</v>
       </c>
     </row>
@@ -6295,15 +6433,16 @@
       <c r="D127" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
         <v>250</v>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6326,15 +6465,16 @@
       <c r="D128" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="n">
         <v>180</v>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6357,15 +6497,16 @@
       <c r="D129" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="n">
         <v>150</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6388,15 +6529,16 @@
       <c r="D130" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="n">
         <v>150</v>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6419,15 +6561,16 @@
       <c r="D131" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="n">
         <v>150</v>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
         <v>140</v>
       </c>
     </row>
@@ -6450,15 +6593,16 @@
       <c r="D132" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="n">
         <v>250</v>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6481,15 +6625,16 @@
       <c r="D133" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="n">
         <v>180</v>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6512,15 +6657,16 @@
       <c r="D134" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
         <v>150</v>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6543,15 +6689,16 @@
       <c r="D135" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="n">
         <v>150</v>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6574,15 +6721,16 @@
       <c r="D136" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="n">
         <v>150</v>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
         <v>140</v>
       </c>
     </row>
@@ -6605,15 +6753,16 @@
       <c r="D137" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="n">
         <v>250</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6636,15 +6785,16 @@
       <c r="D138" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="n">
         <v>180</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6667,15 +6817,16 @@
       <c r="D139" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="n">
         <v>150</v>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6698,15 +6849,16 @@
       <c r="D140" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="n">
         <v>150</v>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6729,15 +6881,16 @@
       <c r="D141" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="n">
         <v>150</v>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
         <v>140</v>
       </c>
     </row>
@@ -6760,15 +6913,16 @@
       <c r="D142" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="n">
         <v>250</v>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6791,15 +6945,16 @@
       <c r="D143" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="n">
         <v>180</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6822,15 +6977,16 @@
       <c r="D144" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="n">
         <v>150</v>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6853,15 +7009,16 @@
       <c r="D145" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="n">
         <v>150</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
         <v>192</v>
       </c>
     </row>
@@ -6884,15 +7041,16 @@
       <c r="D146" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="n">
         <v>150</v>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
         <v>140</v>
       </c>
     </row>
@@ -6915,15 +7073,16 @@
       <c r="D147" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="n">
         <v>250</v>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G147" t="n">
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
         <v>280</v>
       </c>
     </row>
@@ -6946,15 +7105,16 @@
       <c r="D148" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="n">
         <v>180</v>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G148" t="n">
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6977,15 +7137,16 @@
       <c r="D149" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="n">
         <v>150</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7008,15 +7169,16 @@
       <c r="D150" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="n">
         <v>150</v>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7039,15 +7201,16 @@
       <c r="D151" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="n">
         <v>150</v>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G151" t="n">
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
         <v>140</v>
       </c>
     </row>
@@ -7070,15 +7233,16 @@
       <c r="D152" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="n">
         <v>250</v>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G152" t="n">
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7101,15 +7265,16 @@
       <c r="D153" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="n">
         <v>300</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G153" t="n">
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
         <v>160</v>
       </c>
     </row>
@@ -7132,15 +7297,16 @@
       <c r="D154" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="n">
         <v>200</v>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G154" t="n">
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
         <v>140</v>
       </c>
     </row>
@@ -7163,15 +7329,16 @@
       <c r="D155" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="n">
         <v>150</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G155" t="n">
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7194,15 +7361,16 @@
       <c r="D156" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="n">
         <v>250</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G156" t="n">
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7225,15 +7393,16 @@
       <c r="D157" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="n">
         <v>250</v>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G157" t="n">
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7256,15 +7425,16 @@
       <c r="D158" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="n">
         <v>300</v>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G158" t="n">
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
         <v>160</v>
       </c>
     </row>
@@ -7287,15 +7457,16 @@
       <c r="D159" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="n">
         <v>200</v>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G159" t="n">
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
         <v>140</v>
       </c>
     </row>
@@ -7318,15 +7489,16 @@
       <c r="D160" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="n">
         <v>150</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G160" t="n">
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7349,15 +7521,16 @@
       <c r="D161" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="n">
         <v>250</v>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7380,15 +7553,16 @@
       <c r="D162" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="n">
         <v>250</v>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7411,15 +7585,16 @@
       <c r="D163" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="n">
         <v>300</v>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
         <v>160</v>
       </c>
     </row>
@@ -7442,15 +7617,16 @@
       <c r="D164" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="n">
         <v>200</v>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
         <v>140</v>
       </c>
     </row>
@@ -7473,15 +7649,16 @@
       <c r="D165" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="n">
         <v>150</v>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G165" t="n">
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7504,15 +7681,16 @@
       <c r="D166" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="n">
         <v>250</v>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G166" t="n">
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7535,15 +7713,16 @@
       <c r="D167" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="n">
         <v>250</v>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G167" t="n">
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7566,15 +7745,16 @@
       <c r="D168" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="n">
         <v>300</v>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G168" t="n">
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
         <v>160</v>
       </c>
     </row>
@@ -7597,15 +7777,16 @@
       <c r="D169" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="n">
         <v>200</v>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G169" t="n">
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
         <v>140</v>
       </c>
     </row>
@@ -7628,15 +7809,16 @@
       <c r="D170" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="n">
         <v>150</v>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G170" t="n">
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7659,15 +7841,16 @@
       <c r="D171" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="n">
         <v>250</v>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G171" t="n">
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7690,15 +7873,16 @@
       <c r="D172" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="n">
         <v>250</v>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G172" t="n">
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7721,15 +7905,16 @@
       <c r="D173" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="n">
         <v>300</v>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G173" t="n">
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
         <v>160</v>
       </c>
     </row>
@@ -7752,15 +7937,16 @@
       <c r="D174" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="n">
         <v>200</v>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G174" t="n">
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
         <v>140</v>
       </c>
     </row>
@@ -7783,15 +7969,16 @@
       <c r="D175" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="n">
         <v>150</v>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G175" t="n">
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7814,15 +8001,16 @@
       <c r="D176" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="n">
         <v>250</v>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G176" t="n">
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7845,15 +8033,16 @@
       <c r="D177" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="n">
         <v>250</v>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G177" t="n">
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
         <v>280</v>
       </c>
     </row>
@@ -7876,15 +8065,16 @@
       <c r="D178" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="n">
         <v>300</v>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
         <v>160</v>
       </c>
     </row>
@@ -7907,15 +8097,16 @@
       <c r="D179" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E179" t="n">
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="n">
         <v>200</v>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
         <v>140</v>
       </c>
     </row>
@@ -7938,15 +8129,16 @@
       <c r="D180" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
         <v>150</v>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G180" t="n">
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
         <v>192</v>
       </c>
     </row>
@@ -7969,15 +8161,16 @@
       <c r="D181" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="n">
         <v>250</v>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G181" t="n">
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8000,15 +8193,16 @@
       <c r="D182" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E182" t="n">
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="n">
         <v>250</v>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G182" t="n">
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8031,15 +8225,16 @@
       <c r="D183" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E183" t="n">
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="n">
         <v>200</v>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G183" t="n">
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
         <v>140</v>
       </c>
     </row>
@@ -8062,15 +8257,16 @@
       <c r="D184" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E184" t="n">
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="n">
         <v>150</v>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G184" t="n">
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8093,15 +8289,16 @@
       <c r="D185" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E185" t="n">
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="n">
         <v>150</v>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G185" t="n">
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8124,15 +8321,16 @@
       <c r="D186" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="n">
         <v>250</v>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G186" t="n">
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8155,15 +8353,16 @@
       <c r="D187" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="n">
         <v>250</v>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8186,15 +8385,16 @@
       <c r="D188" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E188" t="n">
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="n">
         <v>200</v>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
         <v>140</v>
       </c>
     </row>
@@ -8217,15 +8417,16 @@
       <c r="D189" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E189" t="n">
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="n">
         <v>150</v>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8248,15 +8449,16 @@
       <c r="D190" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="n">
         <v>150</v>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8279,15 +8481,16 @@
       <c r="D191" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E191" t="n">
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="n">
         <v>250</v>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8310,15 +8513,16 @@
       <c r="D192" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="n">
         <v>250</v>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G192" t="n">
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8341,15 +8545,16 @@
       <c r="D193" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E193" t="n">
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="n">
         <v>200</v>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
         <v>140</v>
       </c>
     </row>
@@ -8372,15 +8577,16 @@
       <c r="D194" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="n">
         <v>150</v>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G194" t="n">
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8403,15 +8609,16 @@
       <c r="D195" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="n">
         <v>150</v>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G195" t="n">
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8434,15 +8641,16 @@
       <c r="D196" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="n">
         <v>250</v>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G196" t="n">
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8465,15 +8673,16 @@
       <c r="D197" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E197" t="n">
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="n">
         <v>250</v>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G197" t="n">
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8496,15 +8705,16 @@
       <c r="D198" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E198" t="n">
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="n">
         <v>200</v>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G198" t="n">
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
         <v>140</v>
       </c>
     </row>
@@ -8527,15 +8737,16 @@
       <c r="D199" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E199" t="n">
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="n">
         <v>150</v>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G199" t="n">
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8558,15 +8769,16 @@
       <c r="D200" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E200" t="n">
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
         <v>150</v>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G200" t="n">
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8589,15 +8801,16 @@
       <c r="D201" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E201" t="n">
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="n">
         <v>250</v>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G201" t="n">
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8620,15 +8833,16 @@
       <c r="D202" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E202" t="n">
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="n">
         <v>250</v>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G202" t="n">
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8651,15 +8865,16 @@
       <c r="D203" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
         <v>200</v>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G203" t="n">
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
         <v>140</v>
       </c>
     </row>
@@ -8682,15 +8897,16 @@
       <c r="D204" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E204" t="n">
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
         <v>150</v>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G204" t="n">
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8713,15 +8929,16 @@
       <c r="D205" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E205" t="n">
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="n">
         <v>150</v>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G205" t="n">
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8744,15 +8961,16 @@
       <c r="D206" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="n">
         <v>250</v>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G206" t="n">
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8775,15 +8993,16 @@
       <c r="D207" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="n">
         <v>250</v>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G207" t="n">
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8806,15 +9025,16 @@
       <c r="D208" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="n">
         <v>200</v>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G208" t="n">
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
         <v>140</v>
       </c>
     </row>
@@ -8837,15 +9057,16 @@
       <c r="D209" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="n">
         <v>150</v>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G209" t="n">
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8868,15 +9089,16 @@
       <c r="D210" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="n">
         <v>150</v>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G210" t="n">
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
         <v>192</v>
       </c>
     </row>
@@ -8899,15 +9121,16 @@
       <c r="D211" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="n">
         <v>250</v>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G211" t="n">
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
         <v>280</v>
       </c>
     </row>
@@ -8930,15 +9153,16 @@
       <c r="D212" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="n">
         <v>250</v>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G212" t="n">
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
         <v>384</v>
       </c>
     </row>
@@ -8961,15 +9185,16 @@
       <c r="D213" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="n">
         <v>200</v>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G213" t="n">
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
         <v>140</v>
       </c>
     </row>
@@ -8992,15 +9217,16 @@
       <c r="D214" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="n">
         <v>150</v>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G214" t="n">
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9023,15 +9249,16 @@
       <c r="D215" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="n">
         <v>150</v>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G215" t="n">
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9054,15 +9281,16 @@
       <c r="D216" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="n">
         <v>150</v>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G216" t="n">
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9085,15 +9313,16 @@
       <c r="D217" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E217" t="n">
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="n">
         <v>250</v>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G217" t="n">
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
         <v>384</v>
       </c>
     </row>
@@ -9116,15 +9345,16 @@
       <c r="D218" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="n">
         <v>200</v>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G218" t="n">
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9147,15 +9377,16 @@
       <c r="D219" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="n">
         <v>150</v>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G219" t="n">
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9178,15 +9409,16 @@
       <c r="D220" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="n">
         <v>150</v>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G220" t="n">
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9209,15 +9441,16 @@
       <c r="D221" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="n">
         <v>150</v>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G221" t="n">
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9240,15 +9473,16 @@
       <c r="D222" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="n">
         <v>250</v>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G222" t="n">
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
         <v>384</v>
       </c>
     </row>
@@ -9271,15 +9505,16 @@
       <c r="D223" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="n">
         <v>200</v>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G223" t="n">
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9302,15 +9537,16 @@
       <c r="D224" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="n">
         <v>150</v>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G224" t="n">
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9333,15 +9569,16 @@
       <c r="D225" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="n">
         <v>150</v>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G225" t="n">
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9364,15 +9601,16 @@
       <c r="D226" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="n">
         <v>150</v>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G226" t="n">
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9395,15 +9633,16 @@
       <c r="D227" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="n">
         <v>250</v>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G227" t="n">
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
         <v>384</v>
       </c>
     </row>
@@ -9426,15 +9665,16 @@
       <c r="D228" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="n">
         <v>200</v>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G228" t="n">
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9457,15 +9697,16 @@
       <c r="D229" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E229" t="n">
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="n">
         <v>150</v>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G229" t="n">
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9488,15 +9729,16 @@
       <c r="D230" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="n">
         <v>150</v>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G230" t="n">
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9519,15 +9761,16 @@
       <c r="D231" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E231" t="n">
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="n">
         <v>150</v>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G231" t="n">
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9550,15 +9793,16 @@
       <c r="D232" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="n">
         <v>250</v>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G232" t="n">
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
         <v>384</v>
       </c>
     </row>
@@ -9581,15 +9825,16 @@
       <c r="D233" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E233" t="n">
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="n">
         <v>200</v>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G233" t="n">
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9612,15 +9857,16 @@
       <c r="D234" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E234" t="n">
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="n">
         <v>150</v>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G234" t="n">
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9643,15 +9889,16 @@
       <c r="D235" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="n">
         <v>150</v>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G235" t="n">
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9674,15 +9921,16 @@
       <c r="D236" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="n">
         <v>150</v>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G236" t="n">
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9705,15 +9953,16 @@
       <c r="D237" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="n">
         <v>250</v>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G237" t="n">
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
         <v>384</v>
       </c>
     </row>
@@ -9736,15 +9985,16 @@
       <c r="D238" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="n">
         <v>200</v>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G238" t="n">
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9767,15 +10017,16 @@
       <c r="D239" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="n">
         <v>150</v>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G239" t="n">
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9798,15 +10049,16 @@
       <c r="D240" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="n">
         <v>150</v>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G240" t="n">
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9829,15 +10081,16 @@
       <c r="D241" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="n">
         <v>150</v>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G241" t="n">
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9860,15 +10113,16 @@
       <c r="D242" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="n">
         <v>250</v>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G242" t="n">
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
         <v>280</v>
       </c>
     </row>
@@ -9891,15 +10145,16 @@
       <c r="D243" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E243" t="n">
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="n">
         <v>200</v>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G243" t="n">
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
         <v>140</v>
       </c>
     </row>
@@ -9922,15 +10177,16 @@
       <c r="D244" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E244" t="n">
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="n">
         <v>150</v>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G244" t="n">
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9953,15 +10209,16 @@
       <c r="D245" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E245" t="n">
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="n">
         <v>150</v>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G245" t="n">
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
         <v>192</v>
       </c>
     </row>
@@ -9984,15 +10241,16 @@
       <c r="D246" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E246" t="n">
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="n">
         <v>250</v>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G246" t="n">
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10015,15 +10273,16 @@
       <c r="D247" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="n">
         <v>250</v>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G247" t="n">
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10046,15 +10305,16 @@
       <c r="D248" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="n">
         <v>200</v>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G248" t="n">
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
         <v>140</v>
       </c>
     </row>
@@ -10077,15 +10337,16 @@
       <c r="D249" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="n">
         <v>150</v>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G249" t="n">
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10108,15 +10369,16 @@
       <c r="D250" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="n">
         <v>150</v>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G250" t="n">
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10139,15 +10401,16 @@
       <c r="D251" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="n">
         <v>250</v>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G251" t="n">
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10170,15 +10433,16 @@
       <c r="D252" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="n">
         <v>250</v>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G252" t="n">
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10201,15 +10465,16 @@
       <c r="D253" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="n">
         <v>200</v>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G253" t="n">
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
         <v>140</v>
       </c>
     </row>
@@ -10232,15 +10497,16 @@
       <c r="D254" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="n">
         <v>150</v>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G254" t="n">
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10263,15 +10529,16 @@
       <c r="D255" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="n">
         <v>150</v>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G255" t="n">
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10294,15 +10561,16 @@
       <c r="D256" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="n">
         <v>250</v>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G256" t="n">
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10325,15 +10593,16 @@
       <c r="D257" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="n">
         <v>250</v>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G257" t="n">
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10356,15 +10625,16 @@
       <c r="D258" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E258" t="n">
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="n">
         <v>200</v>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G258" t="n">
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
         <v>140</v>
       </c>
     </row>
@@ -10387,15 +10657,16 @@
       <c r="D259" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E259" t="n">
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="n">
         <v>150</v>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G259" t="n">
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10418,15 +10689,16 @@
       <c r="D260" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="n">
         <v>150</v>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G260" t="n">
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10449,15 +10721,16 @@
       <c r="D261" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E261" t="n">
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="n">
         <v>250</v>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G261" t="n">
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10480,15 +10753,16 @@
       <c r="D262" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="n">
         <v>250</v>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G262" t="n">
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10511,15 +10785,16 @@
       <c r="D263" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E263" t="n">
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="n">
         <v>200</v>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G263" t="n">
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
         <v>140</v>
       </c>
     </row>
@@ -10542,15 +10817,16 @@
       <c r="D264" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E264" t="n">
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="n">
         <v>150</v>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G264" t="n">
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10573,15 +10849,16 @@
       <c r="D265" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E265" t="n">
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="n">
         <v>150</v>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G265" t="n">
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10604,15 +10881,16 @@
       <c r="D266" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E266" t="n">
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="n">
         <v>250</v>
       </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G266" t="n">
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10635,15 +10913,16 @@
       <c r="D267" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E267" t="n">
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="n">
         <v>250</v>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G267" t="n">
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10666,15 +10945,16 @@
       <c r="D268" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E268" t="n">
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="n">
         <v>200</v>
       </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G268" t="n">
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
         <v>140</v>
       </c>
     </row>
@@ -10697,15 +10977,16 @@
       <c r="D269" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E269" t="n">
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="n">
         <v>150</v>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G269" t="n">
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10728,15 +11009,16 @@
       <c r="D270" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E270" t="n">
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="n">
         <v>150</v>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G270" t="n">
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10759,15 +11041,16 @@
       <c r="D271" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E271" t="n">
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="n">
         <v>250</v>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G271" t="n">
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10790,15 +11073,16 @@
       <c r="D272" s="1" t="n">
         <v>46086.1875</v>
       </c>
-      <c r="E272" t="n">
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="n">
         <v>250</v>
       </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G272" t="n">
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10821,15 +11105,16 @@
       <c r="D273" s="1" t="n">
         <v>46086.33333333334</v>
       </c>
-      <c r="E273" t="n">
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="n">
         <v>200</v>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G273" t="n">
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
         <v>140</v>
       </c>
     </row>
@@ -10852,15 +11137,16 @@
       <c r="D274" s="1" t="n">
         <v>46086.45833333334</v>
       </c>
-      <c r="E274" t="n">
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="n">
         <v>150</v>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G274" t="n">
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10883,15 +11169,16 @@
       <c r="D275" s="1" t="n">
         <v>46086.58333333334</v>
       </c>
-      <c r="E275" t="n">
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="n">
         <v>150</v>
       </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G275" t="n">
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
         <v>192</v>
       </c>
     </row>
@@ -10914,15 +11201,16 @@
       <c r="D276" s="1" t="n">
         <v>46086.70833333334</v>
       </c>
-      <c r="E276" t="n">
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="n">
         <v>250</v>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G276" t="n">
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10945,15 +11233,16 @@
       <c r="D277" s="1" t="n">
         <v>46087.1875</v>
       </c>
-      <c r="E277" t="n">
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="n">
         <v>250</v>
       </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G277" t="n">
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
         <v>280</v>
       </c>
     </row>
@@ -10976,15 +11265,16 @@
       <c r="D278" s="1" t="n">
         <v>46087.33333333334</v>
       </c>
-      <c r="E278" t="n">
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="n">
         <v>200</v>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G278" t="n">
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
         <v>140</v>
       </c>
     </row>
@@ -11007,15 +11297,16 @@
       <c r="D279" s="1" t="n">
         <v>46087.45833333334</v>
       </c>
-      <c r="E279" t="n">
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="n">
         <v>150</v>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G279" t="n">
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11038,15 +11329,20 @@
       <c r="D280" s="1" t="n">
         <v>46087.58333333334</v>
       </c>
-      <c r="E280" t="n">
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
         <v>150</v>
       </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G280" t="n">
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11069,15 +11365,16 @@
       <c r="D281" s="1" t="n">
         <v>46087.70833333334</v>
       </c>
-      <c r="E281" t="n">
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="n">
         <v>250</v>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G281" t="n">
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11100,15 +11397,16 @@
       <c r="D282" s="1" t="n">
         <v>46088.1875</v>
       </c>
-      <c r="E282" t="n">
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="n">
         <v>250</v>
       </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G282" t="n">
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11131,15 +11429,16 @@
       <c r="D283" s="1" t="n">
         <v>46088.33333333334</v>
       </c>
-      <c r="E283" t="n">
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="n">
         <v>200</v>
       </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G283" t="n">
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
         <v>140</v>
       </c>
     </row>
@@ -11162,15 +11461,16 @@
       <c r="D284" s="1" t="n">
         <v>46088.45833333334</v>
       </c>
-      <c r="E284" t="n">
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="n">
         <v>150</v>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G284" t="n">
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11193,15 +11493,16 @@
       <c r="D285" s="1" t="n">
         <v>46088.58333333334</v>
       </c>
-      <c r="E285" t="n">
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="n">
         <v>150</v>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G285" t="n">
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11224,15 +11525,16 @@
       <c r="D286" s="1" t="n">
         <v>46088.70833333334</v>
       </c>
-      <c r="E286" t="n">
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="n">
         <v>250</v>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G286" t="n">
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11255,15 +11557,16 @@
       <c r="D287" s="1" t="n">
         <v>46089.1875</v>
       </c>
-      <c r="E287" t="n">
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="n">
         <v>250</v>
       </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G287" t="n">
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11286,15 +11589,16 @@
       <c r="D288" s="1" t="n">
         <v>46089.33333333334</v>
       </c>
-      <c r="E288" t="n">
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="n">
         <v>200</v>
       </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G288" t="n">
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
         <v>140</v>
       </c>
     </row>
@@ -11317,15 +11621,16 @@
       <c r="D289" s="1" t="n">
         <v>46089.45833333334</v>
       </c>
-      <c r="E289" t="n">
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="n">
         <v>150</v>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G289" t="n">
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11348,15 +11653,16 @@
       <c r="D290" s="1" t="n">
         <v>46089.58333333334</v>
       </c>
-      <c r="E290" t="n">
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="n">
         <v>150</v>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G290" t="n">
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11379,15 +11685,16 @@
       <c r="D291" s="1" t="n">
         <v>46089.70833333334</v>
       </c>
-      <c r="E291" t="n">
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="n">
         <v>250</v>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G291" t="n">
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11410,15 +11717,16 @@
       <c r="D292" s="1" t="n">
         <v>46090.1875</v>
       </c>
-      <c r="E292" t="n">
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="n">
         <v>250</v>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G292" t="n">
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11441,15 +11749,16 @@
       <c r="D293" s="1" t="n">
         <v>46090.33333333334</v>
       </c>
-      <c r="E293" t="n">
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="n">
         <v>200</v>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G293" t="n">
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
         <v>140</v>
       </c>
     </row>
@@ -11472,15 +11781,16 @@
       <c r="D294" s="1" t="n">
         <v>46090.45833333334</v>
       </c>
-      <c r="E294" t="n">
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="n">
         <v>150</v>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G294" t="n">
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11503,15 +11813,16 @@
       <c r="D295" s="1" t="n">
         <v>46090.58333333334</v>
       </c>
-      <c r="E295" t="n">
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="n">
         <v>150</v>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G295" t="n">
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11534,15 +11845,16 @@
       <c r="D296" s="1" t="n">
         <v>46090.70833333334</v>
       </c>
-      <c r="E296" t="n">
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="n">
         <v>250</v>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G296" t="n">
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11565,15 +11877,16 @@
       <c r="D297" s="1" t="n">
         <v>46091.1875</v>
       </c>
-      <c r="E297" t="n">
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="n">
         <v>250</v>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G297" t="n">
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11596,15 +11909,16 @@
       <c r="D298" s="1" t="n">
         <v>46091.33333333334</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="n">
         <v>200</v>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G298" t="n">
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
         <v>140</v>
       </c>
     </row>
@@ -11627,15 +11941,16 @@
       <c r="D299" s="1" t="n">
         <v>46091.45833333334</v>
       </c>
-      <c r="E299" t="n">
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="n">
         <v>150</v>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G299" t="n">
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11658,15 +11973,16 @@
       <c r="D300" s="1" t="n">
         <v>46091.58333333334</v>
       </c>
-      <c r="E300" t="n">
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="n">
         <v>150</v>
       </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G300" t="n">
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
         <v>192</v>
       </c>
     </row>
@@ -11689,15 +12005,16 @@
       <c r="D301" s="1" t="n">
         <v>46091.70833333334</v>
       </c>
-      <c r="E301" t="n">
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="n">
         <v>250</v>
       </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="G301" t="n">
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>available</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
         <v>280</v>
       </c>
     </row>
@@ -11712,7 +12029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12230,17 +12547,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>69a9c33fc33095b555984ee7</t>
+          <t>69a9c33fc33095b555984eeb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Kabir Verma</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>customer2246@example.com</t>
+          <t>customer6990@example.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -12334,17 +12651,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>69a9c33fc33095b555984eeb</t>
+          <t>69a9c33fc33095b555984ee7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kabir Verma</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>customer6990@example.com</t>
+          <t>customer2246@example.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -12355,6 +12672,36 @@
       </c>
       <c r="F22" s="1" t="n">
         <v>46086.74592559028</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>69aa610db1032a9eef1ff9a1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mann Shah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>23bca046@sxca.edu.in</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1234567899</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>46087.21349135417</v>
       </c>
     </row>
   </sheetData>
@@ -12976,17 +13323,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eec</t>
+          <t>69a9c340c33095b555984eed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Diya Patel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>customer2246@example.com</t>
+          <t>customer6187@example.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12996,19 +13343,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INOX R-City Mall</t>
+          <t>Sathyam Cinemas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46091.70833333334</v>
+        <v>46088.58333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>389</v>
+        <v>618</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -13020,45 +13367,45 @@
         <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>46086</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eed</t>
+          <t>69a9c340c33095b555984ef0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diya Patel</t>
+          <t>Kabir Verma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customer6187@example.com</t>
+          <t>customer6990@example.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Until Dawn</t>
+          <t>Devara: Part 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sathyam Cinemas</t>
+          <t>INOX R-City Mall</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46088.58333333334</v>
+        <v>46091.45833333334</v>
       </c>
       <c r="H13" t="n">
-        <v>618</v>
+        <v>1317</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -13070,45 +13417,45 @@
         <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>46085</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eee</t>
+          <t>69a9c340c33095b555984eef</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohan Gupta</t>
+          <t>Neha Singh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>customer5689@example.com</t>
+          <t>customer8107@example.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lilo &amp; Stitch</t>
+          <t>Thunderbolts*</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INOX DLF Promenade</t>
+          <t>PVR Forum Mall Koramangala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46087.33333333334</v>
+        <v>46086.33333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -13120,45 +13467,45 @@
         <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>46084</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984eef</t>
+          <t>69a9c340c33095b555984eec</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neha Singh</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>customer8107@example.com</t>
+          <t>customer2246@example.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thunderbolts*</t>
+          <t>Until Dawn</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PVR Forum Mall Koramangala</t>
+          <t>INOX R-City Mall</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46086.33333333334</v>
+        <v>46091.70833333334</v>
       </c>
       <c r="H15" t="n">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -13170,45 +13517,45 @@
         <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>46083</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>69a9c340c33095b555984ef0</t>
+          <t>69a9c340c33095b555984eee</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kabir Verma</t>
+          <t>Rohan Gupta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>customer6990@example.com</t>
+          <t>customer5689@example.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Devara: Part 1</t>
+          <t>Lilo &amp; Stitch</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>INOX R-City Mall</t>
+          <t>INOX DLF Promenade</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46091.45833333334</v>
+        <v>46087.33333333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1317</v>
+        <v>510</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -13220,7 +13567,7 @@
         <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>46082</v>
+        <v>46084</v>
       </c>
     </row>
   </sheetData>
